--- a/data/trans_camb/P68-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P68-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 14,4</t>
+          <t>1,3; 15,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 8,87</t>
+          <t>-5,62; 8,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 6,79</t>
+          <t>-5,5; 7,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 10,08</t>
+          <t>-8,37; 10,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 6,0</t>
+          <t>-11,38; 5,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 7,32</t>
+          <t>-7,44; 8,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 10,95</t>
+          <t>0,46; 11,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 5,61</t>
+          <t>-5,91; 4,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 5,27</t>
+          <t>-4,13; 5,71</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 81,99</t>
+          <t>5,16; 87,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 50,13</t>
+          <t>-23,93; 49,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,21; 37,79</t>
+          <t>-24,71; 41,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,81; 60,27</t>
+          <t>-33,62; 65,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,45; 36,98</t>
+          <t>-45,54; 32,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 46,09</t>
+          <t>-28,26; 53,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 59,95</t>
+          <t>1,77; 61,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 30,74</t>
+          <t>-24,8; 25,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 28,36</t>
+          <t>-17,95; 30,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 3,43</t>
+          <t>-9,7; 1,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 3,75</t>
+          <t>-8,53; 3,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,62; -4,78</t>
+          <t>-22,4; -4,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 11,81</t>
+          <t>-3,89; 10,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 7,34</t>
+          <t>-6,81; 7,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 11,46</t>
+          <t>-0,85; 11,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 3,32</t>
+          <t>-6,0; 3,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 2,58</t>
+          <t>-6,58; 2,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,83; -0,85</t>
+          <t>-16,34; -0,75</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 14,61</t>
+          <t>-34,34; 6,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 17,05</t>
+          <t>-29,95; 13,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,2; -17,87</t>
+          <t>-76,25; -16,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 75,46</t>
+          <t>-17,9; 65,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,81; 47,25</t>
+          <t>-28,55; 47,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 73,42</t>
+          <t>-4,27; 75,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,23; 14,91</t>
+          <t>-22,49; 16,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 11,57</t>
+          <t>-25,06; 11,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-67,72; -4,6</t>
+          <t>-63,77; -3,24</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 4,71</t>
+          <t>-8,81; 5,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 10,2</t>
+          <t>-3,03; 10,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,49; -3,98</t>
+          <t>-16,63; -4,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 11,92</t>
+          <t>-5,31; 11,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 9,69</t>
+          <t>-5,59; 10,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 29,82</t>
+          <t>-2,1; 30,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 4,69</t>
+          <t>-6,21; 5,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 6,9</t>
+          <t>-2,72; 7,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 11,51</t>
+          <t>-8,26; 11,43</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 20,05</t>
+          <t>-28,99; 22,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 44,01</t>
+          <t>-10,38; 43,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-55,09; -16,24</t>
+          <t>-54,74; -16,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 66,09</t>
+          <t>-20,0; 66,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 53,91</t>
+          <t>-20,97; 53,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 160,86</t>
+          <t>-9,19; 167,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 21,02</t>
+          <t>-21,95; 22,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 30,26</t>
+          <t>-9,87; 32,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,53; 49,88</t>
+          <t>-31,59; 50,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 0,44</t>
+          <t>-10,51; 0,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 2,93</t>
+          <t>-8,46; 3,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 2,59</t>
+          <t>-8,5; 2,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 4,43</t>
+          <t>-8,5; 4,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 4,43</t>
+          <t>-9,02; 4,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 5,2</t>
+          <t>-11,77; 5,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -0,09</t>
+          <t>-7,85; 0,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 1,86</t>
+          <t>-6,38; 1,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 2,14</t>
+          <t>-7,88; 1,82</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 1,11</t>
+          <t>-39,37; 1,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-29,52; 13,23</t>
+          <t>-30,03; 14,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 11,95</t>
+          <t>-31,29; 13,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,27; 21,86</t>
+          <t>-33,08; 23,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 23,24</t>
+          <t>-35,48; 20,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,64; 25,25</t>
+          <t>-45,26; 24,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,54; -0,22</t>
+          <t>-30,74; 1,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,96; 8,13</t>
+          <t>-24,46; 9,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 9,07</t>
+          <t>-31,16; 7,78</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,7</t>
+          <t>-4,52; 1,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,84</t>
+          <t>-3,12; 3,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,94; -3,5</t>
+          <t>-13,97; -3,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 4,88</t>
+          <t>-2,52; 5,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,13</t>
+          <t>-4,14; 2,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 9,03</t>
+          <t>-1,67; 8,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,95</t>
+          <t>-2,88; 1,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,86</t>
+          <t>-2,87; 1,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -0,26</t>
+          <t>-7,81; -0,16</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 7,19</t>
+          <t>-17,35; 6,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 11,95</t>
+          <t>-11,86; 14,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-53,73; -14,91</t>
+          <t>-54,49; -14,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 24,42</t>
+          <t>-10,73; 25,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 16,29</t>
+          <t>-17,82; 13,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 44,25</t>
+          <t>-7,71; 43,07</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 8,58</t>
+          <t>-11,55; 8,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 8,37</t>
+          <t>-11,69; 8,21</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,4; -1,14</t>
+          <t>-32,81; -1,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P68-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P68-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>-0,42</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>-0,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 15,63</t>
+          <t>1,55; 14,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 8,97</t>
+          <t>-5,57; 8,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 7,27</t>
+          <t>-7,06; 5,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 10,81</t>
+          <t>-8,28; 9,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 5,36</t>
+          <t>-11,56; 5,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 8,0</t>
+          <t>-7,4; 8,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 11,14</t>
+          <t>-0,41; 11,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 4,76</t>
+          <t>-5,61; 5,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 5,71</t>
+          <t>-5,28; 4,48</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>-2,0%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>-0,01%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 87,62</t>
+          <t>5,73; 80,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,93; 49,74</t>
+          <t>-22,37; 49,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 41,09</t>
+          <t>-28,34; 31,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,62; 65,18</t>
+          <t>-32,78; 57,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 32,42</t>
+          <t>-45,94; 32,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 53,98</t>
+          <t>-28,6; 56,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 61,05</t>
+          <t>-1,59; 63,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 25,88</t>
+          <t>-24,49; 30,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 30,14</t>
+          <t>-21,84; 24,85</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-12,47</t>
+          <t>-5,13</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>4,55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-6,68</t>
+          <t>-1,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 1,45</t>
+          <t>-8,88; 2,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 3,09</t>
+          <t>-8,42; 3,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,4; -4,2</t>
+          <t>-10,59; 0,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 10,33</t>
+          <t>-3,49; 11,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 7,58</t>
+          <t>-6,72; 7,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 11,98</t>
+          <t>-1,63; 11,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 3,6</t>
+          <t>-5,82; 3,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 2,68</t>
+          <t>-6,54; 2,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,34; -0,75</t>
+          <t>-6,2; 2,27</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-47,16%</t>
+          <t>-19,38%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-27,49%</t>
+          <t>-7,03%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 6,15</t>
+          <t>-31,35; 9,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 13,01</t>
+          <t>-28,74; 14,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,25; -16,37</t>
+          <t>-35,72; 3,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 65,3</t>
+          <t>-14,83; 66,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 47,42</t>
+          <t>-28,27; 46,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 75,12</t>
+          <t>-7,0; 70,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 16,37</t>
+          <t>-22,16; 14,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 11,93</t>
+          <t>-24,6; 11,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-63,77; -3,24</t>
+          <t>-23,1; 10,34</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-10,6</t>
+          <t>-9,81</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-6,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 5,13</t>
+          <t>-8,72; 5,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 10,62</t>
+          <t>-3,61; 9,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,63; -4,07</t>
+          <t>-16,32; -3,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 11,69</t>
+          <t>-5,35; 11,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 10,01</t>
+          <t>-5,98; 9,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 30,22</t>
+          <t>-8,47; 6,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 5,21</t>
+          <t>-6,22; 4,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 7,57</t>
+          <t>-2,78; 7,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 11,43</t>
+          <t>-11,23; -1,49</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-39,26%</t>
+          <t>-36,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>-1,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-7,52%</t>
+          <t>-24,19%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 22,43</t>
+          <t>-29,56; 23,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 43,67</t>
+          <t>-12,39; 41,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,74; -16,23</t>
+          <t>-54,8; -15,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,0; 66,04</t>
+          <t>-20,9; 66,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 53,72</t>
+          <t>-23,45; 58,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 167,33</t>
+          <t>-31,1; 36,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 22,57</t>
+          <t>-22,61; 19,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 32,96</t>
+          <t>-10,07; 31,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 50,35</t>
+          <t>-39,84; -6,03</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,21</t>
+          <t>-3,74</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,09</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,31</t>
+          <t>-1,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 0,22</t>
+          <t>-10,71; -0,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 3,11</t>
+          <t>-8,09; 2,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 2,86</t>
+          <t>-9,28; 1,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 4,75</t>
+          <t>-7,73; 4,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 4,29</t>
+          <t>-9,0; 4,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 5,06</t>
+          <t>-4,62; 6,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 0,18</t>
+          <t>-7,85; -0,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 1,99</t>
+          <t>-7,0; 1,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 1,82</t>
+          <t>-5,13; 2,67</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-13,0%</t>
+          <t>-15,15%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-4,76%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-9,66%</t>
+          <t>-6,36%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,37; 1,39</t>
+          <t>-39,28; -1,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 14,22</t>
+          <t>-29,75; 12,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 13,6</t>
+          <t>-33,96; 8,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,08; 23,49</t>
+          <t>-30,24; 23,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 20,08</t>
+          <t>-35,06; 19,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-45,26; 24,4</t>
+          <t>-17,22; 31,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,74; 1,11</t>
+          <t>-30,11; 0,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 9,29</t>
+          <t>-27,56; 6,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 7,78</t>
+          <t>-19,77; 12,75</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-7,45</t>
+          <t>-4,75</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,27</t>
+          <t>-2,28</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 1,51</t>
+          <t>-4,63; 1,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 3,26</t>
+          <t>-3,41; 2,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,97; -3,54</t>
+          <t>-7,93; -1,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 5,0</t>
+          <t>-2,41; 5,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 2,75</t>
+          <t>-4,28; 2,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 8,79</t>
+          <t>-1,58; 4,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,93</t>
+          <t>-3,19; 1,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 1,84</t>
+          <t>-2,93; 1,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,81; -0,16</t>
+          <t>-4,54; -0,17</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-29,88%</t>
+          <t>-19,05%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-13,76%</t>
+          <t>-9,6%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 6,24</t>
+          <t>-17,71; 5,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 14,06</t>
+          <t>-12,86; 11,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,49; -14,68</t>
+          <t>-30,64; -8,17</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 25,53</t>
+          <t>-10,42; 26,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 13,79</t>
+          <t>-18,15; 15,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 43,07</t>
+          <t>-6,63; 23,49</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 8,51</t>
+          <t>-12,67; 7,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 8,21</t>
+          <t>-11,97; 8,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,81; -1,07</t>
+          <t>-18,03; -0,74</t>
         </is>
       </c>
     </row>
